--- a/PSCBOX_S14_갈고리추가.xlsx
+++ b/PSCBOX_S14_갈고리추가.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N240"/>
+  <dimension ref="A1:N257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,6 +1021,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
@@ -2167,6 +2168,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -3358,161 +3360,202 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t># ================= SREBAR (갈고리 열차) ==================================</t>
+          <t>#  --- D3 : 하부슬래브 종방향 철근 (8-243 D3 / D3-1 / D3-2  H16) ---</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>#  srebar | id | code | dia | init x,y,rot | range -,+ | num | ctc | leg |  |  |  | z</t>
+          <t>#  ctc 125 는 **도면 단면의 점을 재서** 나온 값이다 — 상·하면 모두 125.0 ± 0.5 로,</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>#  점이 x = 0, ±125, ±250 … ±3,000 에 떨어진다 (같은 자로 잰 D1 은 250 이 나온다).</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>#  한 줄이 철근 **N 개**다. 종방향과 같은 직선 위를 같은 간격으로 달리므로</t>
+          <t>#  init.y 는 슬래브 «안» 이면 된다 (상면 -6,110 ~ 소피트 -6,853. 가운데가 -6,480).</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>#  lrebar 쪽 문법을 쓰고, 풀리는 것은 보통 횡방향과 같다 (페이지가 trebar N 개로 편다).</t>
+          <t>#  gap  짝 사이 한계. 가운데 두께 743 · 헌치 993 → 벌어짐이 907 까지 가므로 1,000.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>lrebar</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>16</v>
+      </c>
+      <c r="D192" t="n">
+        <v>49</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>0,-6480,0</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-3050,3050</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H192" t="n">
+        <v>125</v>
+      </c>
+      <c r="I192" t="n">
+        <v>300</v>
+      </c>
+      <c r="J192" t="n">
+        <v>100</v>
+      </c>
+      <c r="K192" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>bottom slab  (8-243 D3 H16)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>#  ! 차례가 조립 차례다 — 갈고리는 종방향(lrebar) **뒤에** 와야 종방향에 «걸린다».</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>#    앞에 두면 갈고리가 바깥이 되고 종방향이 그 안에 쌓인다.</t>
+          <t># ================= SREBAR (갈고리 열차) ==================================</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>#  srebar | id | code | dia | init x,y,rot | range -,+ | num | ctc | leg |  |  |  | z</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>#  입력에서 뺀 것 :</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>#    몸통 길이   **장이 낸다.** 도면이 X 를 「206~480 (범위!)」로 적은 것이</t>
+          <t>#  한 줄이 철근 **N 개**다. 종방향과 같은 직선 위를 같은 간격으로 달리므로</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>#                「한 수로 적을 수 없다」는 뜻이고, 그래서 X 는 결과여야 한다.</t>
+          <t>#  lrebar 쪽 문법을 쓰고, 풀리는 것은 보통 횡방향과 같다 (페이지가 trebar N 개로 편다).</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>#    nors       ㄷ 는 정의상 마주보는 두 면을 문다. 다리 방향은 code + rot 이 정하고,</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>#                좌·우는 **x 부호만** 다르다.</t>
+          <t>#  ! 차례가 조립 차례다 — 갈고리는 종방향(lrebar) **뒤에** 와야 종방향에 «걸린다».</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>#    ctcmax·ctcmin  기준이 정하는 한계다 → 입력이 아니라 결과 검사.</t>
+          <t>#    앞에 두면 갈고리가 바깥이 되고 종방향이 그 안에 쌓인다.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>#    gap · path     ㄷ 자체가 짝이고, 경로를 안 탄다.</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>#  입력에서 뺀 것 :</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>#  rot   **꼴의 회전**이다 (= trebar). 열차 방향은 꼴의 «첫 조각»(다리)에서 나온다.</t>
+          <t>#    몸통 길이   **장이 낸다.** 도면이 X 를 「206~480 (범위!)」로 적은 것이</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>#          code 21 : rot  90 → 몸통 세로 · 다리 가로 (열차는 가로로 간다)</t>
+          <t>#                「한 수로 적을 수 없다」는 뜻이고, 그래서 X 는 결과여야 한다.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>#                    rot 180 → 몸통 가로 · 다리 아래 (열차는 세로로 내려간다)</t>
+          <t>#    nors       ㄷ 는 정의상 마주보는 두 면을 문다. 다리 방향은 code + rot 이 정하고,</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>#  leg   다리 길이 = 정착길이. 기준이 정하는 값이라 장 밖이다.</t>
+          <t>#                좌·우는 **x 부호만** 다르다.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>#  z     교축방향 층. 도면에서 ㄷ 는 **점선**이다 — 이 단면에 없다는 뜻이고,</t>
+          <t>#    ctcmax·ctcmin  기준이 정하는 한계다 → 입력이 아니라 결과 검사.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>#        같은 z 끼리만 서로 민다 (종방향은 모든 단면을 뚫으므로 z 와 무관하게 걸린다).</t>
+          <t>#    gap · path     ㄷ 자체가 짝이고, 경로를 안 탄다.</t>
         </is>
       </c>
     </row>
@@ -3526,185 +3569,185 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t># --- T1 : 상부슬래브 ㄷ (몸통 세로. 다리 150 이 상·하 D1 을 문다) ---</t>
+          <t>#  rot   **꼴의 회전**이다 (= trebar). 열차 방향은 꼴의 «첫 조각»(다리)에서 나온다.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>#   8-243 : T1-1 X=164 / T1-2 X=212~486 / T1-3 X=206~480,  H13</t>
+          <t>#          code 21 : rot  90 → 몸통 세로 · 다리 가로 (열차는 가로로 간다)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>#   ctc 500 은 **도면 단면의 타이를 세어서** 나온 값이다 — 간격이 500 ± 2 mm 다</t>
+          <t>#                    rot 180 → 몸통 가로 · 다리 아래 (열차는 세로로 내려간다)</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>#   (같은 방법으로 잰 D1 의 250 구간이 249, 125 구간이 125 로 나와 눈금이 맞는다).</t>
+          <t>#  leg   다리 길이 = 정착길이. 기준이 정하는 값이라 장 밖이다.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>#   num 25 = 데크 12,400 / 500.</t>
+          <t>#  z     교축방향 층. 도면에서 ㄷ 는 **점선**이다 — 이 단면에 없다는 뜻이고,</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>#   init.y 는 슬래브 «안» 이면 된다. 밖이면 엔진이 부재 안으로 끌어들인다</t>
+          <t>#        같은 z 끼리만 서로 민다 (종방향은 모든 단면을 뚫으므로 z 와 무관하게 걸린다).</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>#   (데크가 -3% 라 수평인 직선은 끝에서 슬래브를 벗어난다).</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>#   풀어 보면 몸통이 157 ~ 586 mm 로 나온다 — 선단 157 ↔ 도면 164,</t>
+          <t># --- T1 : 상부슬래브 ㄷ (몸통 세로. 다리 150 이 상·하 D1 을 문다) ---</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>#   가운데 185~428 ↔ 도면 206~486. (복부 위 514~593 은 도면 T1 구간이 아니다.)</t>
+          <t>#   8-243 : T1-1 X=164 / T1-2 X=212~486 / T1-3 X=206~480,  H13</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="C220" t="n">
-        <v>21</v>
-      </c>
-      <c r="D220" t="n">
-        <v>13</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>0,-150,90</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>-6200,6200</t>
-        </is>
-      </c>
-      <c r="G220" t="n">
-        <v>25</v>
-      </c>
-      <c r="H220" t="n">
-        <v>500</v>
-      </c>
-      <c r="I220" t="n">
-        <v>150</v>
-      </c>
-      <c r="M220" t="n">
-        <v>1</v>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>top slab tie  (8-243 T1-1/T1-2/T1-3 H13)</t>
+          <t>#   ctc 500 은 **도면 단면의 타이를 세어서** 나온 값이다 — 간격이 500 ± 2 mm 다</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>#   (같은 방법으로 잰 D1 의 250 구간이 249, 125 구간이 125 로 나와 눈금이 맞는다).</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t># --- T2 : 복부 ㄷ (몸통 가로 = 복부 두께. 다리 150 이 아래로 D2 를 문다) ---</t>
+          <t>#   num 25 = 데크 12,400 / 500.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>#   8-243 : T2 H13 L=700,  몸통 402 + 다리 150 x 2.  41 @ 150 = 6,150 (= 42 개)</t>
+          <t>#   init.y 는 슬래브 «안» 이면 된다. 밖이면 엔진이 부재 안으로 끌어들인다</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>#   init 의 x·y 는 lrebar D2 와 **같은 자리**다.</t>
+          <t>#   (데크가 -3% 라 수평인 직선은 끝에서 슬래브를 벗어난다).</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>#   풀어 보면 몸통이 157 ~ 586 mm 로 나온다 — 선단 157 ↔ 도면 164,</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>#   ! **두 줄로 쪼갠다 — 엇갈려 서야 한다.**</t>
+          <t>#   가운데 185~428 ↔ 도면 206~486. (복부 위 514~593 은 도면 T1 구간이 아니다.)</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>#     다리가 150 인데 간격도 150 이라, 한 켜에 다 세우면 한 ㄷ 의 «다리 끝»이</t>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>21</v>
+      </c>
+      <c r="D227" t="n">
+        <v>13</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>0,-150,90</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-6200,6200</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>25</v>
+      </c>
+      <c r="H227" t="n">
+        <v>500</v>
+      </c>
+      <c r="I227" t="n">
+        <v>150</v>
+      </c>
+      <c r="M227" t="n">
+        <v>1</v>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>top slab tie  (8-243 T1-1/T1-2/T1-3 H13)</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>#     바로 다음 ㄷ 의 «몸통 위»에 선다. 재면 겹침이 -13.0 mm — 정확히 철근 지름이다.</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>#     도면이 이 ㄷ 를 번갈아 다른 색으로 그린 것이 그 뜻이다.</t>
+          <t># --- T2 : 복부 ㄷ (몸통 가로 = 복부 두께. 다리 150 이 아래로 D2 를 문다) ---</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>#     300 간격 두 줄을 150 어긋나게 두고 z 로 가르면 겹침이 0 이 된다.</t>
+          <t>#   8-243 : T2 H13 L=700,  몸통 402 + 다리 150 x 2.  41 @ 150 = 6,150 (= 42 개)</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>#     T1 과 T2 도 서로 다른 z 다 — 간격이 500 과 150 이라 같은 단면에 같이 서지 않는다.</t>
+          <t>#   init 의 x·y 는 lrebar D2 와 **같은 자리**다.</t>
         </is>
       </c>
     </row>
@@ -3718,206 +3761,363 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>#   풀어 보면 몸통이 398.3 mm 로 나온다 (도면 402 · 이론 500 - 2 x (40+6.5) = 407).</t>
+          <t>#   ! **두 줄로 쪼갠다 — 엇갈려 서야 한다.**</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>#   복부가 슬래브로 열리는 꼭대기 몇 자리는 버린다 — 「마주보는 면이 1,500 mm 보다</t>
+          <t>#     다리가 150 인데 간격도 150 이라, 한 켜에 다 세우면 한 ㄷ 의 «다리 끝»이</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>#   멀다」, 곧 그 자리엔 ㄷ 가 설 부재가 없다는 뜻이다 (경고로 나온다).</t>
+          <t>#     바로 다음 ㄷ 의 «몸통 위»에 선다. 재면 겹침이 -13.0 mm — 정확히 철근 지름이다.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="C236" t="n">
-        <v>21</v>
-      </c>
-      <c r="D236" t="n">
-        <v>13</v>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>-3250,-3400,180</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>-4500,4500</t>
-        </is>
-      </c>
-      <c r="G236" t="n">
-        <v>21</v>
-      </c>
-      <c r="H236" t="n">
-        <v>300</v>
-      </c>
-      <c r="I236" t="n">
-        <v>150</v>
-      </c>
-      <c r="M236" t="n">
-        <v>2</v>
-      </c>
-      <c r="N236" t="inlineStr">
-        <is>
-          <t>left  web tie, layer 1  (8-243 T2 H13 L=700)</t>
+          <t>#     도면이 이 ㄷ 를 번갈아 다른 색으로 그린 것이 그 뜻이다.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>T2b</t>
-        </is>
-      </c>
-      <c r="C237" t="n">
-        <v>21</v>
-      </c>
-      <c r="D237" t="n">
-        <v>13</v>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>-3250,-3250,180</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>-4500,4500</t>
-        </is>
-      </c>
-      <c r="G237" t="n">
-        <v>21</v>
-      </c>
-      <c r="H237" t="n">
-        <v>300</v>
-      </c>
-      <c r="I237" t="n">
-        <v>150</v>
-      </c>
-      <c r="M237" t="n">
-        <v>3</v>
-      </c>
-      <c r="N237" t="inlineStr">
-        <is>
-          <t>left  web tie, layer 2 — 150 어긋나게</t>
+          <t>#     300 간격 두 줄을 150 어긋나게 두고 z 로 가르면 겹침이 0 이 된다.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>T2-1</t>
-        </is>
-      </c>
-      <c r="C238" t="n">
-        <v>21</v>
-      </c>
-      <c r="D238" t="n">
-        <v>13</v>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>3250,-3400,180</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>-4500,4500</t>
-        </is>
-      </c>
-      <c r="G238" t="n">
-        <v>21</v>
-      </c>
-      <c r="H238" t="n">
-        <v>300</v>
-      </c>
-      <c r="I238" t="n">
-        <v>150</v>
-      </c>
-      <c r="M238" t="n">
-        <v>2</v>
-      </c>
-      <c r="N238" t="inlineStr">
-        <is>
-          <t>right web tie, layer 1</t>
+          <t>#     T1 과 T2 도 서로 다른 z 다 — 간격이 500 과 150 이라 같은 단면에 같이 서지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>T2-1b</t>
-        </is>
-      </c>
-      <c r="C239" t="n">
-        <v>21</v>
-      </c>
-      <c r="D239" t="n">
-        <v>13</v>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>3250,-3250,180</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>-4500,4500</t>
-        </is>
-      </c>
-      <c r="G239" t="n">
-        <v>21</v>
-      </c>
-      <c r="H239" t="n">
-        <v>300</v>
-      </c>
-      <c r="I239" t="n">
-        <v>150</v>
-      </c>
-      <c r="M239" t="n">
-        <v>3</v>
-      </c>
-      <c r="N239" t="inlineStr">
-        <is>
-          <t>right web tie, layer 2 — 150 어긋나게</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
+        <is>
+          <t>#   풀어 보면 몸통이 398.3 mm 로 나온다 (도면 402 · 이론 500 - 2 x (40+6.5) = 407).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>#   복부가 슬래브로 열리는 꼭대기 몇 자리는 버린다 — 「마주보는 면이 1,500 mm 보다</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>#   멀다」, 곧 그 자리엔 ㄷ 가 설 부재가 없다는 뜻이다 (경고로 나온다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>21</v>
+      </c>
+      <c r="D243" t="n">
+        <v>13</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-3250,-3400,180</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-4500,4500</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>21</v>
+      </c>
+      <c r="H243" t="n">
+        <v>300</v>
+      </c>
+      <c r="I243" t="n">
+        <v>150</v>
+      </c>
+      <c r="M243" t="n">
+        <v>2</v>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>left  web tie, layer 1  (8-243 T2 H13 L=700)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>T2b</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>21</v>
+      </c>
+      <c r="D244" t="n">
+        <v>13</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-3250,-3250,180</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-4500,4500</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>21</v>
+      </c>
+      <c r="H244" t="n">
+        <v>300</v>
+      </c>
+      <c r="I244" t="n">
+        <v>150</v>
+      </c>
+      <c r="M244" t="n">
+        <v>3</v>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>left  web tie, layer 2 — 150 어긋나게</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>T2-1</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>21</v>
+      </c>
+      <c r="D245" t="n">
+        <v>13</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>3250,-3400,180</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-4500,4500</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>21</v>
+      </c>
+      <c r="H245" t="n">
+        <v>300</v>
+      </c>
+      <c r="I245" t="n">
+        <v>150</v>
+      </c>
+      <c r="M245" t="n">
+        <v>2</v>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>right web tie, layer 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>T2-1b</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>21</v>
+      </c>
+      <c r="D246" t="n">
+        <v>13</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>3250,-3250,180</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-4500,4500</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>21</v>
+      </c>
+      <c r="H246" t="n">
+        <v>300</v>
+      </c>
+      <c r="I246" t="n">
+        <v>150</v>
+      </c>
+      <c r="M246" t="n">
+        <v>3</v>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>right web tie, layer 2 — 150 어긋나게</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t># --- T3 : 하부슬래브 ㄷ (몸통 세로 = 슬래브 두께. 다리 150 이 상·하 D3 을 문다) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>#   ctc 450 은 **도면 단면의 타이를 세어서** 나온 값이다 (85.0 px x 5.30 = 450 ± 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>#   num 14 = 6,100 / 450.   z 4 — T1(1) · T2(2,3) 와 다른 켜다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>#   ! 도면의 T3 는 **∩** 다 : 몸통이 상면을 따라 387 mm 가고 다리 둘이 소피트까지</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>#     내려가 아래 D3 를 문다. 지금 `srebar` 는 「몸통 = 마주보는 두 면 · 다리 = 입력」</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>#     만 적을 수 있어 그 꼴을 **못 적는다** (STATUS 「아직 안 한 것」).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>#     여기서는 같은 일을 하는 **T1 꼴**로 넣는다 — 몸통이 두께를 가로지르고</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>#     다리 150 이 상·하 D3 을 문다. 몸통이 670(가운데) ~ 923(헌치) 으로 나온다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>21</v>
+      </c>
+      <c r="D256" t="n">
+        <v>13</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>0,-6480,90</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>-3050,3050</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>14</v>
+      </c>
+      <c r="H256" t="n">
+        <v>450</v>
+      </c>
+      <c r="I256" t="n">
+        <v>150</v>
+      </c>
+      <c r="M256" t="n">
+        <v>4</v>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>bottom slab tie  (8-243 T3 H13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_S14_갈고리추가.xlsx
+++ b/PSCBOX_S14_갈고리추가.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N257"/>
+  <dimension ref="A1:N255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>T2b</t>
+          <t>T2-1</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>-3250,-3250,180</t>
+          <t>3250,-3400,180</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -3910,214 +3910,124 @@
         <v>150</v>
       </c>
       <c r="M244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>left  web tie, layer 2 — 150 어긋나게</t>
+          <t>right web tie, layer 1</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>T2-1</t>
-        </is>
-      </c>
-      <c r="C245" t="n">
-        <v>21</v>
-      </c>
-      <c r="D245" t="n">
-        <v>13</v>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>3250,-3400,180</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>-4500,4500</t>
-        </is>
-      </c>
-      <c r="G245" t="n">
-        <v>21</v>
-      </c>
-      <c r="H245" t="n">
-        <v>300</v>
-      </c>
-      <c r="I245" t="n">
-        <v>150</v>
-      </c>
-      <c r="M245" t="n">
-        <v>2</v>
-      </c>
-      <c r="N245" t="inlineStr">
-        <is>
-          <t>right web tie, layer 1</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>T2-1b</t>
-        </is>
-      </c>
-      <c r="C246" t="n">
-        <v>21</v>
-      </c>
-      <c r="D246" t="n">
-        <v>13</v>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>3250,-3250,180</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>-4500,4500</t>
-        </is>
-      </c>
-      <c r="G246" t="n">
-        <v>21</v>
-      </c>
-      <c r="H246" t="n">
-        <v>300</v>
-      </c>
-      <c r="I246" t="n">
-        <v>150</v>
-      </c>
-      <c r="M246" t="n">
-        <v>3</v>
-      </c>
-      <c r="N246" t="inlineStr">
-        <is>
-          <t>right web tie, layer 2 — 150 어긋나게</t>
+          <t># --- T3 : 하부슬래브 ㄷ (몸통 세로 = 슬래브 두께. 다리 150 이 상·하 D3 을 문다) ---</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>#   ctc 450 은 **도면 단면의 타이를 세어서** 나온 값이다 (85.0 px x 5.30 = 450 ± 2).</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t># --- T3 : 하부슬래브 ㄷ (몸통 세로 = 슬래브 두께. 다리 150 이 상·하 D3 을 문다) ---</t>
+          <t>#   num 14 = 6,100 / 450.   z 4 — T1(1) · T2(2,3) 와 다른 켜다.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>#   ctc 450 은 **도면 단면의 타이를 세어서** 나온 값이다 (85.0 px x 5.30 = 450 ± 2).</t>
+          <t>#   ! 도면의 T3 는 **∩** 다 : 몸통이 상면을 따라 387 mm 가고 다리 둘이 소피트까지</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>#   num 14 = 6,100 / 450.   z 4 — T1(1) · T2(2,3) 와 다른 켜다.</t>
+          <t>#     내려가 아래 D3 를 문다. 지금 `srebar` 는 「몸통 = 마주보는 두 면 · 다리 = 입력」</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>#   ! 도면의 T3 는 **∩** 다 : 몸통이 상면을 따라 387 mm 가고 다리 둘이 소피트까지</t>
+          <t>#     만 적을 수 있어 그 꼴을 **못 적는다** (STATUS 「아직 안 한 것」).</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>#     내려가 아래 D3 를 문다. 지금 `srebar` 는 「몸통 = 마주보는 두 면 · 다리 = 입력」</t>
+          <t>#     여기서는 같은 일을 하는 **T1 꼴**로 넣는다 — 몸통이 두께를 가로지르고</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>#     만 적을 수 있어 그 꼴을 **못 적는다** (STATUS 「아직 안 한 것」).</t>
+          <t>#     다리 150 이 상·하 D3 을 문다. 몸통이 670(가운데) ~ 923(헌치) 으로 나온다.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>#     여기서는 같은 일을 하는 **T1 꼴**로 넣는다 — 몸통이 두께를 가로지르고</t>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>21</v>
+      </c>
+      <c r="D254" t="n">
+        <v>13</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>0,-6480,180</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>-2800,2800</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>13</v>
+      </c>
+      <c r="H254" t="n">
+        <v>450</v>
+      </c>
+      <c r="J254" t="n">
+        <v>387</v>
+      </c>
+      <c r="M254" t="n">
+        <v>4</v>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>bottom slab tie — ∩ (8-243 T3 H13, 몸통 387)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
-        <is>
-          <t>#     다리 150 이 상·하 D3 을 문다. 몸통이 670(가운데) ~ 923(헌치) 으로 나온다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="C256" t="n">
-        <v>21</v>
-      </c>
-      <c r="D256" t="n">
-        <v>13</v>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>0,-6480,90</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>-3050,3050</t>
-        </is>
-      </c>
-      <c r="G256" t="n">
-        <v>14</v>
-      </c>
-      <c r="H256" t="n">
-        <v>450</v>
-      </c>
-      <c r="I256" t="n">
-        <v>150</v>
-      </c>
-      <c r="M256" t="n">
-        <v>4</v>
-      </c>
-      <c r="N256" t="inlineStr">
-        <is>
-          <t>bottom slab tie  (8-243 T3 H13)</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_S14_갈고리추가.xlsx
+++ b/PSCBOX_S14_갈고리추가.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="323">
   <si>
     <t># PSCBOX  --  S14 (segment next to the pier)   *** 2D TEST ***</t>
   </si>
@@ -799,7 +799,19 @@
     <t>#    gap · path     ㄷ 자체가 짝이고, 경로를 안 탄다.</t>
   </si>
   <si>
-    <t>#  rot   **꼴의 회전**이다 (= trebar). 열차 방향은 꼴의 «첫 조각»(다리)에서 나온다.</t>
+    <t>#  code  **어느 개념인지는 code 가 말한다.** 21 과 21a 는 **같은 모양으로 굽는**</t>
+  </si>
+  <si>
+    <t>#          철근이다 (치수 비율만 다르다) — 가공표에는 둘 다 21 로 나간다.</t>
+  </si>
+  <si>
+    <t>#          그런데 엔진에서는 뜻이 갈린다 :  21 = ㄷ (몸통이 늘어난다 · leg 를 적는다)</t>
+  </si>
+  <si>
+    <t>#          21a = ∩ (다리가 늘어난다 · body 를 적는다 · 제 면에 수직으로 선다)</t>
+  </si>
+  <si>
+    <t>#  rot   **꼴의 회전**이다 (= trebar). 열차 방향은 꼴의 «첫 조각»에서 나온다.</t>
   </si>
   <si>
     <t>#          code 21 : rot  90 → 몸통 세로 · 다리 가로 (열차는 가로로 간다)</t>
@@ -808,6 +820,12 @@
     <t>#                    rot 180 → 몸통 가로 · 다리 아래 (열차는 세로로 내려간다)</t>
   </si>
   <si>
+    <t>#          ! 21a 는 **자리마다 제 면의 기울기만큼 더 돌아간다** — 하부슬래브</t>
+  </si>
+  <si>
+    <t>#            상면이 꺾인 폴리라인이라 rot 하나로는 다리가 면에 수직이 안 된다.</t>
+  </si>
+  <si>
     <t>#  leg·body  **빈칸이 «콘크리트가 정하는 쪽» 이다.** 둘 중 하나만 적는다 —</t>
   </si>
   <si>
@@ -950,6 +968,9 @@
   </si>
   <si>
     <t>T3</t>
+  </si>
+  <si>
+    <t>21a</t>
   </si>
   <si>
     <t>0,-6480,180</t>
@@ -1304,7 +1325,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:N260"/>
+  <dimension ref="A1:N266"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1744,7 +1765,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>58</v>
@@ -2615,7 +2635,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>108</v>
@@ -3690,37 +3709,37 @@
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>5</v>
+        <v>272</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>277</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
@@ -3738,184 +3757,124 @@
         <v>280</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>281</v>
       </c>
-      <c r="B232" t="s">
-        <v>282</v>
-      </c>
-      <c r="C232">
-        <v>21</v>
-      </c>
-      <c r="D232">
-        <v>13</v>
-      </c>
-      <c r="E232" t="s">
-        <v>283</v>
-      </c>
-      <c r="F232" t="s">
-        <v>214</v>
-      </c>
-      <c r="G232">
-        <v>25</v>
-      </c>
-      <c r="H232">
-        <v>500</v>
-      </c>
-      <c r="I232">
-        <v>150</v>
-      </c>
-      <c r="M232">
-        <v>1</v>
-      </c>
-      <c r="N232" t="s">
-        <v>284</v>
-      </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>5</v>
+        <v>282</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
+        <v>287</v>
+      </c>
+      <c r="B238" t="s">
         <v>288</v>
+      </c>
+      <c r="C238">
+        <v>21</v>
+      </c>
+      <c r="D238">
+        <v>13</v>
+      </c>
+      <c r="E238" t="s">
+        <v>289</v>
+      </c>
+      <c r="F238" t="s">
+        <v>214</v>
+      </c>
+      <c r="G238">
+        <v>25</v>
+      </c>
+      <c r="H238">
+        <v>500</v>
+      </c>
+      <c r="I238">
+        <v>150</v>
+      </c>
+      <c r="M238">
+        <v>1</v>
+      </c>
+      <c r="N238" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>289</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>293</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>5</v>
+        <v>294</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>281</v>
-      </c>
-      <c r="B248" t="s">
-        <v>297</v>
-      </c>
-      <c r="C248">
-        <v>21</v>
-      </c>
-      <c r="D248">
-        <v>13</v>
-      </c>
-      <c r="E248" t="s">
         <v>298</v>
       </c>
-      <c r="F248" t="s">
-        <v>234</v>
-      </c>
-      <c r="G248">
-        <v>21</v>
-      </c>
-      <c r="H248">
-        <v>300</v>
-      </c>
-      <c r="I248">
-        <v>150</v>
-      </c>
-      <c r="M248">
-        <v>2</v>
-      </c>
-      <c r="N248" t="s">
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
         <v>299</v>
-      </c>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
-        <v>281</v>
-      </c>
-      <c r="B249" t="s">
-        <v>300</v>
-      </c>
-      <c r="C249">
-        <v>21</v>
-      </c>
-      <c r="D249">
-        <v>13</v>
-      </c>
-      <c r="E249" t="s">
-        <v>301</v>
-      </c>
-      <c r="F249" t="s">
-        <v>234</v>
-      </c>
-      <c r="G249">
-        <v>21</v>
-      </c>
-      <c r="H249">
-        <v>300</v>
-      </c>
-      <c r="I249">
-        <v>150</v>
-      </c>
-      <c r="M249">
-        <v>2</v>
-      </c>
-      <c r="N249" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
@@ -3925,32 +3884,92 @@
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>287</v>
+      </c>
+      <c r="B254" t="s">
+        <v>303</v>
+      </c>
+      <c r="C254">
+        <v>21</v>
+      </c>
+      <c r="D254">
+        <v>13</v>
+      </c>
+      <c r="E254" t="s">
+        <v>304</v>
+      </c>
+      <c r="F254" t="s">
+        <v>234</v>
+      </c>
+      <c r="G254">
+        <v>21</v>
+      </c>
+      <c r="H254">
+        <v>300</v>
+      </c>
+      <c r="I254">
+        <v>150</v>
+      </c>
+      <c r="M254">
+        <v>2</v>
+      </c>
+      <c r="N254" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>287</v>
+      </c>
+      <c r="B255" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
+      <c r="C255">
+        <v>21</v>
+      </c>
+      <c r="D255">
+        <v>13</v>
+      </c>
+      <c r="E255" t="s">
         <v>307</v>
+      </c>
+      <c r="F255" t="s">
+        <v>234</v>
+      </c>
+      <c r="G255">
+        <v>21</v>
+      </c>
+      <c r="H255">
+        <v>300</v>
+      </c>
+      <c r="I255">
+        <v>150</v>
+      </c>
+      <c r="M255">
+        <v>2</v>
+      </c>
+      <c r="N255" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>308</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
@@ -3963,44 +3982,74 @@
         <v>310</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>281</v>
-      </c>
-      <c r="B259" t="s">
         <v>311</v>
-      </c>
-      <c r="C259">
-        <v>21</v>
-      </c>
-      <c r="D259">
-        <v>13</v>
-      </c>
-      <c r="E259" t="s">
-        <v>312</v>
-      </c>
-      <c r="F259" t="s">
-        <v>313</v>
-      </c>
-      <c r="G259">
-        <v>13</v>
-      </c>
-      <c r="H259">
-        <v>450</v>
-      </c>
-      <c r="J259">
-        <v>387</v>
-      </c>
-      <c r="M259">
-        <v>4</v>
-      </c>
-      <c r="N259" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
         <v>315</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>287</v>
+      </c>
+      <c r="B265" t="s">
+        <v>317</v>
+      </c>
+      <c r="C265" t="s">
+        <v>318</v>
+      </c>
+      <c r="D265">
+        <v>13</v>
+      </c>
+      <c r="E265" t="s">
+        <v>319</v>
+      </c>
+      <c r="F265" t="s">
+        <v>320</v>
+      </c>
+      <c r="G265">
+        <v>13</v>
+      </c>
+      <c r="H265">
+        <v>450</v>
+      </c>
+      <c r="J265">
+        <v>387</v>
+      </c>
+      <c r="M265">
+        <v>4</v>
+      </c>
+      <c r="N265" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/PSCBOX_S14_갈고리추가.xlsx
+++ b/PSCBOX_S14_갈고리추가.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="330">
   <si>
     <t># PSCBOX  --  S14 (segment next to the pier)   *** 2D TEST ***</t>
   </si>
@@ -763,7 +763,7 @@
     <t># ================= SREBAR (갈고리 열차) ==================================</t>
   </si>
   <si>
-    <t>#  srebar | id | code | dia | init x,y,rot | range -,+ | num | ctc | leg | body |  |  | z</t>
+    <t>#  srebar | id | code | dia | init x,y,rot | range -,+ | num | ctc | leg | body | end |  | z</t>
   </si>
   <si>
     <t>#  한 줄이 철근 **N 개**다. 종방향과 같은 직선 위를 같은 간격으로 달리므로</t>
@@ -844,6 +844,24 @@
     <t>#                   → body 를 적고 leg 를 비운다.  다리는 철근줄에서 철근줄까지다</t>
   </si>
   <si>
+    <t>#  end   **∩ 의 자유단이 어디서 멈추나.** 21a 에만 적는다 (ㄷ 는 leg 가 정한다).</t>
+  </si>
+  <si>
+    <t>#          face  맞은편 면의 **피복선**까지. 두 면이 기울면 두 다리 길이가 달라지고,</t>
+  </si>
+  <si>
+    <t>#                그 다름이 곧 「벽체 경사를 맞춘다」다 — **복부**의 ∩ 가 이것.</t>
+  </si>
+  <si>
+    <t>#          bar   그 자리에서 **가장 가까운 종방향**까지 — **하부슬래브**의 ∩ 가 이것.</t>
+  </si>
+  <si>
+    <t>#          ! 앉는 «자리» 가 아니라 **끝막음**이다. ∩ 의 다리는 두 면에 수직이라</t>
+  </si>
+  <si>
+    <t>#            그 면들에 앉을 수가 없다 (재면 rest 가 빈다). 둘 다 다리 길이를 정하는 자다.</t>
+  </si>
+  <si>
     <t>#  z     교축방향 층. 도면에서 ㄷ 는 **점선**이다 — 이 단면에 없다는 뜻이고,</t>
   </si>
   <si>
@@ -977,6 +995,9 @@
   </si>
   <si>
     <t>-2800,2800</t>
+  </si>
+  <si>
+    <t>bar</t>
   </si>
   <si>
     <t>bottom slab tie — ∩ (8-243 T3 H13, 몸통 387)</t>
@@ -1325,7 +1346,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:N266"/>
+  <dimension ref="A1:N272"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1765,6 +1786,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>58</v>
@@ -2635,6 +2657,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>108</v>
@@ -3739,37 +3762,37 @@
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>5</v>
+        <v>278</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>283</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
@@ -3787,184 +3810,124 @@
         <v>286</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>287</v>
       </c>
-      <c r="B238" t="s">
-        <v>288</v>
-      </c>
-      <c r="C238">
-        <v>21</v>
-      </c>
-      <c r="D238">
-        <v>13</v>
-      </c>
-      <c r="E238" t="s">
-        <v>289</v>
-      </c>
-      <c r="F238" t="s">
-        <v>214</v>
-      </c>
-      <c r="G238">
-        <v>25</v>
-      </c>
-      <c r="H238">
-        <v>500</v>
-      </c>
-      <c r="I238">
-        <v>150</v>
-      </c>
-      <c r="M238">
-        <v>1</v>
-      </c>
-      <c r="N238" t="s">
-        <v>290</v>
-      </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>5</v>
+        <v>288</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>293</v>
+      </c>
+      <c r="B244" t="s">
         <v>294</v>
+      </c>
+      <c r="C244">
+        <v>21</v>
+      </c>
+      <c r="D244">
+        <v>13</v>
+      </c>
+      <c r="E244" t="s">
+        <v>295</v>
+      </c>
+      <c r="F244" t="s">
+        <v>214</v>
+      </c>
+      <c r="G244">
+        <v>25</v>
+      </c>
+      <c r="H244">
+        <v>500</v>
+      </c>
+      <c r="I244">
+        <v>150</v>
+      </c>
+      <c r="M244">
+        <v>1</v>
+      </c>
+      <c r="N244" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>295</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>299</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>5</v>
+        <v>300</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>287</v>
-      </c>
-      <c r="B254" t="s">
-        <v>303</v>
-      </c>
-      <c r="C254">
-        <v>21</v>
-      </c>
-      <c r="D254">
-        <v>13</v>
-      </c>
-      <c r="E254" t="s">
         <v>304</v>
       </c>
-      <c r="F254" t="s">
-        <v>234</v>
-      </c>
-      <c r="G254">
-        <v>21</v>
-      </c>
-      <c r="H254">
-        <v>300</v>
-      </c>
-      <c r="I254">
-        <v>150</v>
-      </c>
-      <c r="M254">
-        <v>2</v>
-      </c>
-      <c r="N254" t="s">
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
         <v>305</v>
-      </c>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>287</v>
-      </c>
-      <c r="B255" t="s">
-        <v>306</v>
-      </c>
-      <c r="C255">
-        <v>21</v>
-      </c>
-      <c r="D255">
-        <v>13</v>
-      </c>
-      <c r="E255" t="s">
-        <v>307</v>
-      </c>
-      <c r="F255" t="s">
-        <v>234</v>
-      </c>
-      <c r="G255">
-        <v>21</v>
-      </c>
-      <c r="H255">
-        <v>300</v>
-      </c>
-      <c r="I255">
-        <v>150</v>
-      </c>
-      <c r="M255">
-        <v>2</v>
-      </c>
-      <c r="N255" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
@@ -3974,32 +3937,92 @@
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>293</v>
+      </c>
+      <c r="B260" t="s">
+        <v>309</v>
+      </c>
+      <c r="C260">
+        <v>21</v>
+      </c>
+      <c r="D260">
+        <v>13</v>
+      </c>
+      <c r="E260" t="s">
+        <v>310</v>
+      </c>
+      <c r="F260" t="s">
+        <v>234</v>
+      </c>
+      <c r="G260">
+        <v>21</v>
+      </c>
+      <c r="H260">
+        <v>300</v>
+      </c>
+      <c r="I260">
+        <v>150</v>
+      </c>
+      <c r="M260">
+        <v>2</v>
+      </c>
+      <c r="N260" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>293</v>
+      </c>
+      <c r="B261" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
+      <c r="C261">
+        <v>21</v>
+      </c>
+      <c r="D261">
+        <v>13</v>
+      </c>
+      <c r="E261" t="s">
         <v>313</v>
+      </c>
+      <c r="F261" t="s">
+        <v>234</v>
+      </c>
+      <c r="G261">
+        <v>21</v>
+      </c>
+      <c r="H261">
+        <v>300</v>
+      </c>
+      <c r="I261">
+        <v>150</v>
+      </c>
+      <c r="M261">
+        <v>2</v>
+      </c>
+      <c r="N261" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>314</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
@@ -4012,44 +4035,77 @@
         <v>316</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>287</v>
-      </c>
-      <c r="B265" t="s">
         <v>317</v>
-      </c>
-      <c r="C265" t="s">
-        <v>318</v>
-      </c>
-      <c r="D265">
-        <v>13</v>
-      </c>
-      <c r="E265" t="s">
-        <v>319</v>
-      </c>
-      <c r="F265" t="s">
-        <v>320</v>
-      </c>
-      <c r="G265">
-        <v>13</v>
-      </c>
-      <c r="H265">
-        <v>450</v>
-      </c>
-      <c r="J265">
-        <v>387</v>
-      </c>
-      <c r="M265">
-        <v>4</v>
-      </c>
-      <c r="N265" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
         <v>322</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>293</v>
+      </c>
+      <c r="B271" t="s">
+        <v>323</v>
+      </c>
+      <c r="C271" t="s">
+        <v>324</v>
+      </c>
+      <c r="D271">
+        <v>13</v>
+      </c>
+      <c r="E271" t="s">
+        <v>325</v>
+      </c>
+      <c r="F271" t="s">
+        <v>326</v>
+      </c>
+      <c r="G271">
+        <v>13</v>
+      </c>
+      <c r="H271">
+        <v>450</v>
+      </c>
+      <c r="J271">
+        <v>387</v>
+      </c>
+      <c r="K271" t="s">
+        <v>327</v>
+      </c>
+      <c r="M271">
+        <v>4</v>
+      </c>
+      <c r="N271" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/PSCBOX_S14_갈고리추가.xlsx
+++ b/PSCBOX_S14_갈고리추가.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="334">
   <si>
     <t># PSCBOX  --  S14 (segment next to the pier)   *** 2D TEST ***</t>
   </si>
@@ -844,22 +844,34 @@
     <t>#                   → body 를 적고 leg 를 비운다.  다리는 철근줄에서 철근줄까지다</t>
   </si>
   <si>
-    <t>#  end   **∩ 의 자유단이 어디서 멈추나.** 21a 에만 적는다 (ㄷ 는 leg 가 정한다).</t>
-  </si>
-  <si>
-    <t>#          face  맞은편 면의 **피복선**까지. 두 면이 기울면 두 다리 길이가 달라지고,</t>
-  </si>
-  <si>
-    <t>#                그 다름이 곧 「벽체 경사를 맞춘다」다 — **복부**의 ∩ 가 이것.</t>
-  </si>
-  <si>
-    <t>#          bar   그 자리에서 **가장 가까운 종방향**까지 — **하부슬래브**의 ∩ 가 이것.</t>
-  </si>
-  <si>
-    <t>#          ! 앉는 «자리» 가 아니라 **끝막음**이다. ∩ 의 다리는 두 면에 수직이라</t>
-  </si>
-  <si>
-    <t>#            그 면들에 앉을 수가 없다 (재면 rest 가 빈다). 둘 다 다리 길이를 정하는 자다.</t>
+    <t>#  end   **다리가 벽체를 어느 쪽으로 찾나.** 21a 에만 적는다 (ㄷ 는 leg 가 정한다).</t>
+  </si>
+  <si>
+    <t>#          normal   다리가 면을 **따라 눕는다** → 제 **법선**으로 벽체를 찾는다.</t>
+  </si>
+  <si>
+    <t>#                   면에 안기므로 두 다리가 각자 제 면을 따라 줄어들고, 그 다름이</t>
+  </si>
+  <si>
+    <t>#                   곧 「벽체 경사를 맞춘다」다.                  ← **복부**의 ∩</t>
+  </si>
+  <si>
+    <t>#          tangent  다리가 두께를 **가로지른다** → 법선은 옆을 보고 그 쪽엔 쓸 면이</t>
+  </si>
+  <si>
+    <t>#                   없다 (재면 rest 가 빈다). **접선**(다리가 뻗는 쪽)으로 찾는다.</t>
+  </si>
+  <si>
+    <t>#                   끝은 앞에 있는 종방향에 기대고, 없으면 그 면의 피복선에서 멈춘다.</t>
+  </si>
+  <si>
+    <t>#                                                            ← **하부슬래브**의 ∩</t>
+  </si>
+  <si>
+    <t>#          ! 「끝단의 어디를 정착시킬 것인가」가 이 한 칸이다 :</t>
+  </si>
+  <si>
+    <t>#            법선이면 다리의 **옆**이, 접선이면 다리의 **끝**이 자리를 잡는다.</t>
   </si>
   <si>
     <t>#  z     교축방향 층. 도면에서 ㄷ 는 **점선**이다 — 이 단면에 없다는 뜻이고,</t>
@@ -997,7 +1009,7 @@
     <t>-2800,2800</t>
   </si>
   <si>
-    <t>bar</t>
+    <t>tangent</t>
   </si>
   <si>
     <t>bottom slab tie — ∩ (8-243 T3 H13, 몸통 387)</t>
@@ -1346,7 +1358,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:N272"/>
+  <dimension ref="A1:N276"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -3792,27 +3804,27 @@
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>5</v>
+        <v>284</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>287</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
@@ -3840,59 +3852,59 @@
         <v>292</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>293</v>
       </c>
-      <c r="B244" t="s">
-        <v>294</v>
-      </c>
-      <c r="C244">
-        <v>21</v>
-      </c>
-      <c r="D244">
-        <v>13</v>
-      </c>
-      <c r="E244" t="s">
-        <v>295</v>
-      </c>
-      <c r="F244" t="s">
-        <v>214</v>
-      </c>
-      <c r="G244">
-        <v>25</v>
-      </c>
-      <c r="H244">
-        <v>500</v>
-      </c>
-      <c r="I244">
-        <v>150</v>
-      </c>
-      <c r="M244">
-        <v>1</v>
-      </c>
-      <c r="N244" t="s">
-        <v>296</v>
-      </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>5</v>
+        <v>294</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>297</v>
+      </c>
+      <c r="B248" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
+      <c r="C248">
+        <v>21</v>
+      </c>
+      <c r="D248">
+        <v>13</v>
+      </c>
+      <c r="E248" t="s">
         <v>299</v>
+      </c>
+      <c r="F248" t="s">
+        <v>214</v>
+      </c>
+      <c r="G248">
+        <v>25</v>
+      </c>
+      <c r="H248">
+        <v>500</v>
+      </c>
+      <c r="I248">
+        <v>150</v>
+      </c>
+      <c r="M248">
+        <v>1</v>
+      </c>
+      <c r="N248" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
@@ -3902,22 +3914,22 @@
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>303</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
@@ -3932,117 +3944,117 @@
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>5</v>
+        <v>306</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>293</v>
-      </c>
-      <c r="B260" t="s">
-        <v>309</v>
-      </c>
-      <c r="C260">
-        <v>21</v>
-      </c>
-      <c r="D260">
-        <v>13</v>
-      </c>
-      <c r="E260" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
         <v>310</v>
-      </c>
-      <c r="F260" t="s">
-        <v>234</v>
-      </c>
-      <c r="G260">
-        <v>21</v>
-      </c>
-      <c r="H260">
-        <v>300</v>
-      </c>
-      <c r="I260">
-        <v>150</v>
-      </c>
-      <c r="M260">
-        <v>2</v>
-      </c>
-      <c r="N260" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>293</v>
-      </c>
-      <c r="B261" t="s">
-        <v>312</v>
-      </c>
-      <c r="C261">
-        <v>21</v>
-      </c>
-      <c r="D261">
-        <v>13</v>
-      </c>
-      <c r="E261" t="s">
-        <v>313</v>
-      </c>
-      <c r="F261" t="s">
-        <v>234</v>
-      </c>
-      <c r="G261">
-        <v>21</v>
-      </c>
-      <c r="H261">
-        <v>300</v>
-      </c>
-      <c r="I261">
-        <v>150</v>
-      </c>
-      <c r="M261">
-        <v>2</v>
-      </c>
-      <c r="N261" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>5</v>
+        <v>311</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>297</v>
+      </c>
+      <c r="B264" t="s">
+        <v>313</v>
+      </c>
+      <c r="C264">
+        <v>21</v>
+      </c>
+      <c r="D264">
+        <v>13</v>
+      </c>
+      <c r="E264" t="s">
+        <v>314</v>
+      </c>
+      <c r="F264" t="s">
+        <v>234</v>
+      </c>
+      <c r="G264">
+        <v>21</v>
+      </c>
+      <c r="H264">
+        <v>300</v>
+      </c>
+      <c r="I264">
+        <v>150</v>
+      </c>
+      <c r="M264">
+        <v>2</v>
+      </c>
+      <c r="N264" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>297</v>
+      </c>
+      <c r="B265" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
+      <c r="C265">
+        <v>21</v>
+      </c>
+      <c r="D265">
+        <v>13</v>
+      </c>
+      <c r="E265" t="s">
         <v>317</v>
+      </c>
+      <c r="F265" t="s">
+        <v>234</v>
+      </c>
+      <c r="G265">
+        <v>21</v>
+      </c>
+      <c r="H265">
+        <v>300</v>
+      </c>
+      <c r="I265">
+        <v>150</v>
+      </c>
+      <c r="M265">
+        <v>2</v>
+      </c>
+      <c r="N265" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>318</v>
+        <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
@@ -4065,47 +4077,67 @@
         <v>322</v>
       </c>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>293</v>
-      </c>
-      <c r="B271" t="s">
         <v>323</v>
-      </c>
-      <c r="C271" t="s">
-        <v>324</v>
-      </c>
-      <c r="D271">
-        <v>13</v>
-      </c>
-      <c r="E271" t="s">
-        <v>325</v>
-      </c>
-      <c r="F271" t="s">
-        <v>326</v>
-      </c>
-      <c r="G271">
-        <v>13</v>
-      </c>
-      <c r="H271">
-        <v>450</v>
-      </c>
-      <c r="J271">
-        <v>387</v>
-      </c>
-      <c r="K271" t="s">
-        <v>327</v>
-      </c>
-      <c r="M271">
-        <v>4</v>
-      </c>
-      <c r="N271" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>297</v>
+      </c>
+      <c r="B275" t="s">
+        <v>327</v>
+      </c>
+      <c r="C275" t="s">
+        <v>328</v>
+      </c>
+      <c r="D275">
+        <v>13</v>
+      </c>
+      <c r="E275" t="s">
         <v>329</v>
+      </c>
+      <c r="F275" t="s">
+        <v>330</v>
+      </c>
+      <c r="G275">
+        <v>13</v>
+      </c>
+      <c r="H275">
+        <v>450</v>
+      </c>
+      <c r="J275">
+        <v>387</v>
+      </c>
+      <c r="K275" t="s">
+        <v>331</v>
+      </c>
+      <c r="M275">
+        <v>4</v>
+      </c>
+      <c r="N275" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>333</v>
       </c>
     </row>
   </sheetData>
